--- a/data/trans_orig/cron_index-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/cron_index-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de cronicidad total</t>
+          <t>Índice de cronicidad total (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,42 +716,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,02</t>
+          <t>0,88; 1,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,38</t>
+          <t>1,17; 1,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 1,31</t>
+          <t>1,11; 1,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 1,87</t>
+          <t>1,56; 1,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,39</t>
+          <t>1,23; 1,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 1,62</t>
+          <t>1,44; 1,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 1,62</t>
+          <t>1,41; 1,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 2,26</t>
+          <t>2,03; 2,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 1,49</t>
+          <t>1,36; 1,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,45</t>
+          <t>1,31; 1,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 2,06</t>
+          <t>1,87; 2,05</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,34</t>
+          <t>0,27; 0,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -866,12 +866,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,49</t>
+          <t>0,42; 0,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,8</t>
+          <t>0,48; 0,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,53</t>
+          <t>0,45; 0,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,5</t>
+          <t>0,72; 1,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,41</t>
+          <t>0,36; 0,42</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,18</t>
+          <t>0,68; 1,15</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,37</t>
+          <t>0,25; 0,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,44</t>
+          <t>0,26; 0,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,27 +1011,27 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,82</t>
+          <t>0,64; 0,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,38</t>
+          <t>0,25; 0,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,41</t>
+          <t>0,27; 0,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,46</t>
+          <t>0,32; 0,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,71</t>
+          <t>0,57; 0,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,74</t>
+          <t>0,62; 0,73</t>
         </is>
       </c>
     </row>
@@ -1136,22 +1136,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,54</t>
+          <t>0,48; 0,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>0,59; 0,66</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>0,58; 0,66</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,58; 0,66</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 0,94</t>
+          <t>0,67; 0,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 0,86</t>
+          <t>0,77; 0,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,49</t>
+          <t>1,01; 1,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,2</t>
+          <t>0,9; 1,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/cron_index-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/cron_index-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,71</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,14</t>
+          <t>2,12</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>1,91</t>
         </is>
       </c>
     </row>
@@ -726,12 +726,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 1,32</t>
+          <t>1,11; 1,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 1,85</t>
+          <t>1,49; 1,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 1,62</t>
+          <t>1,43; 1,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 2,25</t>
+          <t>2,02; 2,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 1,48</t>
+          <t>1,36; 1,49</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,46</t>
+          <t>1,31; 1,45</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 2,05</t>
+          <t>1,83; 2,0</t>
         </is>
       </c>
     </row>
@@ -803,29 +803,29 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>0,77</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,35</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0,49</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>0,7</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,35</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,49</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0,95</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
           <t>0,33</t>
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,74</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,35</t>
+          <t>0,28; 0,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,5</t>
+          <t>0,41; 0,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,8</t>
+          <t>0,72; 0,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,38</t>
+          <t>0,32; 0,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,53</t>
+          <t>0,45; 0,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,48</t>
+          <t>0,66; 0,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,42</t>
+          <t>0,36; 0,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,15</t>
+          <t>0,7; 0,77</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,7</t>
         </is>
       </c>
     </row>
@@ -996,27 +996,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,37</t>
+          <t>0,25; 0,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,43</t>
+          <t>0,27; 0,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,51</t>
+          <t>0,36; 0,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 0,82</t>
+          <t>0,66; 0,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,39</t>
+          <t>0,26; 0,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,47</t>
+          <t>0,32; 0,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,7</t>
+          <t>0,59; 0,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,46</t>
+          <t>0,35; 0,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,73</t>
+          <t>0,65; 0,76</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>0,96</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,54</t>
+          <t>0,47; 0,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,66</t>
+          <t>0,58; 0,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 0,93</t>
+          <t>0,86; 0,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1166,12 +1166,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 0,8</t>
+          <t>0,72; 0,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,48</t>
+          <t>0,96; 1,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,18</t>
+          <t>0,93; 0,99</t>
         </is>
       </c>
     </row>
